--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-10-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_18-10-2025.xlsx
@@ -591,25 +591,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -642,7 +642,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>£11.94</t>
+          <t>£9.95</t>
         </is>
       </c>
     </row>
@@ -712,25 +712,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -763,7 +763,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>£13.52</t>
+          <t>£11.27</t>
         </is>
       </c>
     </row>
@@ -833,25 +833,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -884,7 +884,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>£17.46</t>
+          <t>£14.55</t>
         </is>
       </c>
     </row>
@@ -954,25 +954,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>£17.82</t>
+          <t>£14.85</t>
         </is>
       </c>
     </row>
@@ -1075,25 +1075,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>£22.68</t>
+          <t>£18.90</t>
         </is>
       </c>
     </row>
@@ -1196,25 +1196,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -1247,7 +1247,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>£24.84</t>
+          <t>£20.70</t>
         </is>
       </c>
     </row>
@@ -1317,25 +1317,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>£24.84</t>
+          <t>£20.70</t>
         </is>
       </c>
     </row>
@@ -1438,25 +1438,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>£28.68</t>
+          <t>£23.79</t>
         </is>
       </c>
     </row>
@@ -1559,25 +1559,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>£31.08</t>
+          <t>£25.78</t>
         </is>
       </c>
     </row>
@@ -1680,25 +1680,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>£30.66</t>
+          <t>£25.45</t>
         </is>
       </c>
     </row>
@@ -1801,25 +1801,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>£39.95</t>
+          <t>£33.29</t>
         </is>
       </c>
     </row>
@@ -1922,25 +1922,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -1973,7 +1973,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>£37.68</t>
+          <t>£31.11</t>
         </is>
       </c>
     </row>
@@ -2043,25 +2043,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>£47.64</t>
+          <t>£38.18</t>
         </is>
       </c>
     </row>
@@ -2164,25 +2164,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -2285,25 +2285,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>£45.90</t>
+          <t>£38.13</t>
         </is>
       </c>
     </row>
@@ -2503,25 +2503,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Error: could not convert string to float: '1,150.00'</t>
+          <t>£958.33 Pre Sale Price-£1,040.00</t>
         </is>
       </c>
     </row>
@@ -2624,25 +2624,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -2675,7 +2675,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>£36.00</t>
+          <t>£30.00</t>
         </is>
       </c>
     </row>
@@ -2745,25 +2745,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>£43.00</t>
+          <t>£35.83</t>
         </is>
       </c>
     </row>
@@ -2866,25 +2866,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>£49.00</t>
+          <t>£40.83</t>
         </is>
       </c>
     </row>
@@ -2987,25 +2987,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>£55.00</t>
+          <t>£45.83</t>
         </is>
       </c>
     </row>
@@ -3108,25 +3108,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>£53.08</t>
+          <t>£44.23</t>
         </is>
       </c>
     </row>
@@ -3229,25 +3229,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>£58.87</t>
+          <t>£49.06</t>
         </is>
       </c>
     </row>
@@ -3350,25 +3350,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -3471,25 +3471,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=141.0.7390.108); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6737fe9e5+80021]
-	GetHandleVerifier [0x0x7ff6737fea40+80112]
-	(No symbol) [0x0x7ff67358060f]
-	(No symbol) [0x0x7ff6735d8854]
-	(No symbol) [0x0x7ff6735d8b1c]
-	(No symbol) [0x0x7ff67362c927]
-	(No symbol) [0x0x7ff67360126f]
-	(No symbol) [0x0x7ff67362968a]
-	(No symbol) [0x0x7ff673601003]
-	(No symbol) [0x0x7ff6735c95d1]
-	(No symbol) [0x0x7ff6735ca3f3]
-	GetHandleVerifier [0x0x7ff673abdd8d+2960445]
-	GetHandleVerifier [0x0x7ff673ab804a+2936570]
-	GetHandleVerifier [0x0x7ff673ad8a87+3070263]
-	GetHandleVerifier [0x0x7ff6738184ce+185214]
-	GetHandleVerifier [0x0x7ff67381ff1f+216527]
-	GetHandleVerifier [0x0x7ff673807c24+117460]
-	GetHandleVerifier [0x0x7ff673807ddf+117903]
-	GetHandleVerifier [0x0x7ff6737edcb8+11112]
+	GetHandleVerifier [0x0x7ff712d8e9e5+80021]
+	GetHandleVerifier [0x0x7ff712d8ea40+80112]
+	(No symbol) [0x0x7ff712b1060f]
+	(No symbol) [0x0x7ff712b68854]
+	(No symbol) [0x0x7ff712b68b1c]
+	(No symbol) [0x0x7ff712bbc927]
+	(No symbol) [0x0x7ff712b9126f]
+	(No symbol) [0x0x7ff712bb968a]
+	(No symbol) [0x0x7ff712b91003]
+	(No symbol) [0x0x7ff712b595d1]
+	(No symbol) [0x0x7ff712b5a3f3]
+	GetHandleVerifier [0x0x7ff71304dd8d+2960445]
+	GetHandleVerifier [0x0x7ff71304804a+2936570]
+	GetHandleVerifier [0x0x7ff713068a87+3070263]
+	GetHandleVerifier [0x0x7ff712da84ce+185214]
+	GetHandleVerifier [0x0x7ff712daff1f+216527]
+	GetHandleVerifier [0x0x7ff712d97c24+117460]
+	GetHandleVerifier [0x0x7ff712d97ddf+117903]
+	GetHandleVerifier [0x0x7ff712d7dcb8+11112]
 	BaseThreadInitThunk [0x0x7ffe93dfe8d7+23]
 	RtlUserThreadStart [0x0x7ffe9552c53c+44]
 </t>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>£57.35</t>
+          <t>£47.79</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>£1424.0</t>
+          <t>£1123.52</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>£1544.0</t>
+          <t>£1248.32</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>£1577.92</t>
+          <t>£1220.0</t>
         </is>
       </c>
     </row>
